--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488117_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488117_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.1782</v>
+        <v>7.3985</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1202</v>
+        <v>2.6775</v>
       </c>
       <c r="F2" t="n">
-        <v>5.058</v>
+        <v>4.721</v>
       </c>
       <c r="G2" t="n">
         <v>3.5066</v>
@@ -610,13 +610,13 @@
         <v>5.352</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9669</v>
+        <v>0.1872</v>
       </c>
       <c r="T2" t="n">
-        <v>2.056</v>
+        <v>0.6133</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0891</v>
+        <v>-0.4261</v>
       </c>
       <c r="V2" t="n">
         <v>0.5331</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9473</v>
+        <v>6.6657</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8282</v>
+        <v>7.4623</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8809</v>
+        <v>-0.7966</v>
       </c>
       <c r="G3" t="n">
         <v>8.853</v>
@@ -688,13 +688,13 @@
         <v>1.9822</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5003</v>
+        <v>-0.7819</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6129</v>
+        <v>0.0212</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8874</v>
+        <v>-0.8031</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2071</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2224</v>
+        <v>3.895</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1349</v>
+        <v>0.6672</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0874</v>
+        <v>3.2278</v>
       </c>
       <c r="G4" t="n">
         <v>-0.8798</v>
@@ -766,13 +766,13 @@
         <v>4.5591</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2587</v>
+        <v>0.4139</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1613</v>
+        <v>0.3709</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0974</v>
+        <v>0.043</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1924</v>
+        <v>2.9729</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7554</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9478</v>
+        <v>3.5641</v>
       </c>
       <c r="G5" t="n">
         <v>2.2576</v>
@@ -844,13 +844,13 @@
         <v>2.7751</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6067</v>
+        <v>0.3872</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0586</v>
+        <v>0.1057</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6653</v>
+        <v>0.2816</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2666</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>A. MARTIN BONNEMAISON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5945</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.513</v>
+        <v>0.6388</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1072</v>
+        <v>-0.0443</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3711</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4616</v>
+        <v>-0.1575</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0905</v>
+        <v>0.8647</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3326</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7668</v>
+        <v>0.0404</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4342</v>
+        <v>0.7232</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0385</v>
+        <v>-0.0563</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6948</v>
+        <v>-0.1979</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6563</v>
+        <v>0.1415</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3787</v>
+        <v>0.3964</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1644</v>
+        <v>-0.8462</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.121</v>
+        <v>-0.1248</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0434</v>
+        <v>-0.7214</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2666</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MARTIN BONNEMAISON</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5383</v>
+        <v>0.5757</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6388</v>
+        <v>-0.7562</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1004</v>
+        <v>1.3319</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.3711</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1575</v>
+        <v>1.4616</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8647</v>
+        <v>-1.0905</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.3326</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0404</v>
+        <v>0.7668</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7232</v>
+        <v>-0.4342</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0563</v>
+        <v>0.0385</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1979</v>
+        <v>0.6948</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1415</v>
+        <v>-0.6563</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3964</v>
+        <v>2.3787</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9023</v>
+        <v>-1.183</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1248</v>
+        <v>-0.3642</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7775</v>
+        <v>-0.8187</v>
       </c>
       <c r="V7" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X7" t="n">
-        <v>0.337</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.18</v>
+        <v>0.4846</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.064</v>
+        <v>0.1003</v>
       </c>
       <c r="F8" t="n">
-        <v>0.244</v>
+        <v>0.3844</v>
       </c>
       <c r="G8" t="n">
         <v>0.7375</v>
@@ -1078,13 +1078,13 @@
         <v>2.3787</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0223</v>
+        <v>-0.7177</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0772</v>
+        <v>0.2415</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0995</v>
+        <v>-0.9591</v>
       </c>
       <c r="V8" t="n">
         <v>0.2666</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5961</v>
+        <v>-0.4889</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7206</v>
+        <v>-3.6976</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1245</v>
+        <v>3.2087</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3513</v>
@@ -1156,13 +1156,13 @@
         <v>3.7662</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2448</v>
+        <v>-0.1376</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2458</v>
+        <v>-0.2229</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001</v>
+        <v>0.0852</v>
       </c>
       <c r="V9" t="n">
         <v>1.2071</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.025</v>
+        <v>-1.3723</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4214</v>
+        <v>-2.5441</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3964</v>
+        <v>1.1718</v>
       </c>
       <c r="G10" t="n">
         <v>-2.779</v>
@@ -1234,13 +1234,13 @@
         <v>3.9645</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0998</v>
+        <v>0.7526</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7267</v>
+        <v>0.1506</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8265</v>
+        <v>0.6019</v>
       </c>
       <c r="V10" t="n">
         <v>-0.337</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>20.2318</v>
+        <v>20.7257</v>
       </c>
       <c r="E11" t="n">
-        <v>3.247699999999999</v>
+        <v>3.957000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>16.984</v>
+        <v>16.7688</v>
       </c>
       <c r="G11" t="n">
         <v>10.4229</v>
@@ -1312,13 +1312,13 @@
         <v>27.5529</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.4194</v>
+        <v>-1.9255</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08210000000000006</v>
+        <v>0.7913000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.5015</v>
+        <v>-2.7167</v>
       </c>
       <c r="V11" t="n">
         <v>0.5330999999999999</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. GUZMAN SALINAS</t>
+          <t>L. RUEDA SANTAELLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2956</v>
+        <v>-0.2831</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2605</v>
+        <v>-0.426</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0351</v>
+        <v>0.1429</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6475</v>
+        <v>1.7846</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.7796</v>
+        <v>-0.0615</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4271</v>
+        <v>1.8461</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1569</v>
+        <v>3.6791</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9094</v>
+        <v>1.0636</v>
       </c>
       <c r="L12" t="n">
-        <v>5.0663</v>
+        <v>2.6154</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5094</v>
+        <v>-1.8944</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8702</v>
+        <v>-1.1251</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6392</v>
+        <v>-0.7693</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7929</v>
+        <v>-4.3609</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.1716</v>
+        <v>-6.1449</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3787</v>
+        <v>1.784</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1502</v>
+        <v>0.8195</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2458</v>
+        <v>0.9032</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0956</v>
+        <v>-0.0837</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. MATEO HINOJO</t>
+          <t>W. HASSAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.5832000000000001</v>
+        <v>-0.3826</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3342</v>
+        <v>-1.3796</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.249</v>
+        <v>0.9969</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0917</v>
+        <v>-0.2005</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2677</v>
+        <v>-1.0748</v>
       </c>
       <c r="I13" t="n">
-        <v>0.176</v>
+        <v>0.8743</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0402</v>
+        <v>0.3777</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.3298</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0402</v>
+        <v>0.048</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1319</v>
+        <v>-0.5782</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2677</v>
+        <v>-1.4046</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1358</v>
+        <v>0.8264</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9911</v>
+        <v>0.7929</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4996</v>
+        <v>-0.1753</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6167</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1171</v>
+        <v>0.3927</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.7997</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.7997</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. RUEDA SANTAELLA</t>
+          <t>A. GUZMAN SALINAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7043</v>
+        <v>-0.5144</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0185</v>
+        <v>-0.3624</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6858</v>
+        <v>-0.152</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7846</v>
+        <v>0.6475</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0615</v>
+        <v>-3.7796</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8461</v>
+        <v>4.4271</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6791</v>
+        <v>3.1569</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0636</v>
+        <v>-1.9094</v>
       </c>
       <c r="L14" t="n">
-        <v>2.6154</v>
+        <v>5.0663</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8944</v>
+        <v>-2.5094</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1251</v>
+        <v>-1.8702</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7693</v>
+        <v>-0.6392</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.3609</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.1449</v>
+        <v>-3.1716</v>
       </c>
       <c r="R14" t="n">
-        <v>1.784</v>
+        <v>2.3787</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3983</v>
+        <v>-0.369</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3107</v>
+        <v>-0.3477</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9123</v>
+        <v>-0.0213</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1367</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>G. MARTINEZ LAJARA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8171</v>
+        <v>-0.8204</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2031</v>
+        <v>-0.5995</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.614</v>
+        <v>-0.2209</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.3171</v>
+        <v>-0.7709</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.1142</v>
+        <v>-0.2677</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.203</v>
+        <v>-0.5031</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2643</v>
+        <v>-0.639</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9812</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2455</v>
+        <v>-0.639</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5814</v>
+        <v>-0.1319</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1329</v>
+        <v>-0.2677</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4485</v>
+        <v>0.1358</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1805</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8281</v>
+        <v>-0.0496</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4465</v>
+        <v>0.0395</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3816</v>
+        <v>-0.089</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W. HASSAN</t>
+          <t>P. MATEO HINOJO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8711</v>
+        <v>-0.9626</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6852</v>
+        <v>-0.7417</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8141</v>
+        <v>-0.2209</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2005</v>
+        <v>-0.0917</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0748</v>
+        <v>-0.2677</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8743</v>
+        <v>0.176</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3777</v>
+        <v>0.0402</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3298</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.048</v>
+        <v>0.0402</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5782</v>
+        <v>-0.1319</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4046</v>
+        <v>-0.2677</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8264</v>
+        <v>0.1358</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7929</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6637999999999999</v>
+        <v>0.1202</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8736</v>
+        <v>0.2093</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2098</v>
+        <v>-0.089</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7997</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. MARTINEZ LAJARA</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9504</v>
+        <v>-1.2925</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7013</v>
+        <v>-0.8143</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.249</v>
+        <v>-0.4782</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7709</v>
+        <v>-2.3171</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2677</v>
+        <v>-2.1142</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5031</v>
+        <v>-0.203</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.639</v>
+        <v>0.2643</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-0.9812</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.639</v>
+        <v>1.2455</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1319</v>
+        <v>-2.5814</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2677</v>
+        <v>-1.1329</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1358</v>
+        <v>-1.4485</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1795</v>
+        <v>1.3527</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0624</v>
+        <v>0.8353</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1171</v>
+        <v>0.5174</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7369</v>
+        <v>-1.4209</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5427</v>
+        <v>-1.339</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1943</v>
+        <v>-0.0819</v>
       </c>
       <c r="G18" t="n">
         <v>0.6403</v>
@@ -1858,13 +1858,13 @@
         <v>0.1982</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.2772</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1872</v>
+        <v>0.0165</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.406</v>
+        <v>-0.2937</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5074</v>
+        <v>-2.2469</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2958</v>
+        <v>-2.8456</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2116</v>
+        <v>0.5987</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4445</v>
+        <v>-0.8327</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2545</v>
+        <v>-0.7638</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.19</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0025</v>
+        <v>2.2824</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6728</v>
+        <v>0.9086</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6752</v>
+        <v>1.3738</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.442</v>
+        <v>-3.1151</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9272</v>
+        <v>-1.6723</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5148</v>
+        <v>-1.4428</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5858</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3787</v>
+        <v>-5.1538</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7929</v>
+        <v>2.7751</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2563</v>
+        <v>0.9645</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8187</v>
+        <v>0.0259</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5625</v>
+        <v>0.9386</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. KOYANOUBA DJIRANGAYE</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8529</v>
+        <v>-2.3168</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8977</v>
+        <v>-1.6014</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9552</v>
+        <v>-0.7153</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5682</v>
+        <v>-1.4445</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3691</v>
+        <v>-0.2545</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1991</v>
+        <v>-1.19</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2074</v>
+        <v>-0.0025</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3759</v>
+        <v>0.6728</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1685</v>
+        <v>-0.6752</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3608</v>
+        <v>-1.442</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9932</v>
+        <v>-0.9272</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3676</v>
+        <v>-0.5148</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.7751</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.1538</v>
+        <v>-2.3787</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3787</v>
+        <v>0.7929</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2306</v>
+        <v>0.447</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9898</v>
+        <v>0.5131</v>
       </c>
       <c r="U20" t="n">
-        <v>1.2408</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7403</v>
+        <v>0.2666</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4737</v>
+        <v>0.2666</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.2139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>E. KOYANOUBA DJIRANGAYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8888</v>
+        <v>-3.9297</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6605</v>
+        <v>-2.7127</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7717000000000001</v>
+        <v>-1.217</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8327</v>
+        <v>-1.5682</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7638</v>
+        <v>-1.3691</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.1991</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2824</v>
+        <v>-0.2074</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9086</v>
+        <v>-0.3759</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3738</v>
+        <v>0.1685</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.1151</v>
+        <v>-1.3608</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6723</v>
+        <v>-0.9932</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4428</v>
+        <v>-0.3676</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.3787</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q21" t="n">
         <v>-5.1538</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7751</v>
+        <v>2.3787</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3226</v>
+        <v>2.1538</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7891</v>
+        <v>1.1749</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1117</v>
+        <v>0.979</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-3.2139</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.2987</v>
+        <v>-5.2992</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.1613</v>
+        <v>-5.9388</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1374</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-5.9178</v>
@@ -2170,13 +2170,13 @@
         <v>1.9822</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9844000000000001</v>
+        <v>1.0151</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9029</v>
+        <v>0.3196</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.6955</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-21.5064</v>
+        <v>-19.4691</v>
       </c>
       <c r="E23" t="n">
-        <v>-18.7608</v>
+        <v>-18.761</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7456</v>
+        <v>-0.7081000000000002</v>
       </c>
       <c r="G23" t="n">
         <v>-10.071</v>
@@ -2218,10 +2218,10 @@
         <v>-13.5238</v>
       </c>
       <c r="I23" t="n">
-        <v>3.4527</v>
+        <v>3.452700000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>5.698699999999999</v>
+        <v>5.698700000000001</v>
       </c>
       <c r="K23" t="n">
         <v>-2.8733</v>
@@ -2248,13 +2248,13 @@
         <v>15.8578</v>
       </c>
       <c r="S23" t="n">
-        <v>3.9644</v>
+        <v>6.0017</v>
       </c>
       <c r="T23" t="n">
-        <v>3.1214</v>
+        <v>3.1216</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8428999999999999</v>
+        <v>2.8803</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5330999999999999</v>
